--- a/toolkit-specs/QRAMM_120_questions.xlsx
+++ b/toolkit-specs/QRAMM_120_questions.xlsx
@@ -277,7 +277,7 @@
 • Reviews of TLS settings or certificate usage in cloud-facing systems
 • Cloud Security Posture Management (CSPM) tools identifying crypto parameters in cloud environments
 • Real-time scanning or API-based monitoring of cryptographic configurations in multi-cloud or SaaS environments
-• Contractual obligations for vendors to report cryptographic changes and vulnerabilities ## Stream B: Advanced (40%)</t>
+• Contractual obligations for vendors to report cryptographic changes and vulnerabilities</t>
   </si>
   <si>
     <t>Advanced (40%)</t>
@@ -330,7 +330,7 @@
 • Documentation of prioritization criteria and the systems prioritized for upgrade
 • Quantum risk register tracking asset-level vulnerability and exposure
 • Cross-functional prioritization criteria agreed upon by business and security teams
-• Simulation results or scenario modeling of quantum decryption impacts on key systems ### Level 3 - Established</t>
+• Simulation results or scenario modeling of quantum decryption impacts on key systems</t>
   </si>
   <si>
     <t>How is cryptographic asset inventory maintained over time?</t>
@@ -355,7 +355,7 @@
 • Automated discovery tools integrated with CI/CD pipelines and asset management systems
 • Scheduled re-scans or audits to detect new or modified cryptographic implementations
 • Change management processes requiring cryptographic inventory updates upon deployment
-• Version-controlled inventory logs with timestamps and responsible owner annotations ### Level 4 - Advanced</t>
+• Version-controlled inventory logs with timestamps and responsible owner annotations</t>
   </si>
   <si>
     <t>How does your organization include IoT and embedded devices in its cryptographic inventory and quantum readiness planning?</t>
@@ -402,7 +402,7 @@
 • List of monitored sources (e.g., NIST, IACR, ETSI, arXiv) for cryptographic and quantum updates
 • Scheduled review cycles or internal briefings on cryptographic standards and research
 • Subscriptions to automated alerts or newsletters tracking algorithm deprecation and quantum milestones
-• Tooling or dashboards that flag relevant changes in cryptographic threat landscapes ## Practice 1.2: Vulnerability Assessment &amp; Classification **Outcome**: A systematic approach to identifying, assessing, and classifying cryptographic vulnerabilities to quantum attacks, enabling risk-based prioritization and effective mitigation planning. ## Stream A: Foundation (60%)</t>
+• Tooling or dashboards that flag relevant changes in cryptographic threat landscapes</t>
   </si>
   <si>
     <t>1.2: Vulnerability Assessment &amp; Classification</t>
@@ -480,7 +480,7 @@
 • Comparison of scan results across multiple tools to identify false positives or gaps
 • Use of cryptographic linting or static analysis tools during code reviews to confirm proper implementation
 • Tracking how often flagged vulnerabilities are reclassified or dismissed after deeper inspection
-• Internal guidelines defining when a finding requires expert cryptographic review versus automated confirmation ### Level 4 - Advanced</t>
+• Internal guidelines defining when a finding requires expert cryptographic review versus automated confirmation</t>
   </si>
   <si>
     <t>How does your organization integrate emerging quantum threats into planning and strategy?</t>
@@ -505,7 +505,7 @@
 • Meeting minutes or strategy documentation showing use of quantum threat scenarios in planning
 • Vendor assessments or questionnaires tracking quantum-readiness milestones
 • Migration plans that adjust timelines based on evolving quantum risk forecasts
-• Modeling or simulations used to prioritize systems based on quantum impact and business risk ### Level 5 - Optimizing</t>
+• Modeling or simulations used to prioritize systems based on quantum impact and business risk</t>
   </si>
   <si>
     <t>How does your organization contribute to (quantum) cryptanalysis and mitigation research?</t>
@@ -530,7 +530,7 @@
 • Published papers or blog posts analyzing quantum risks in specific cryptographic algorithms
 • Open-source tools or datasets released for vulnerability testing or analysis
 • Sponsorship of research grants, internships, or academic projects on post-quantum security
-• Internal lab results or testbed simulations exploring weaknesses in legacy protocols or modeling attacks on cryptosystems ## Stream B: Advanced (40%)</t>
+• Internal lab results or testbed simulations exploring weaknesses in legacy protocols or modeling attacks on cryptosystems</t>
   </si>
   <si>
     <t>How are vulnerability findings communicated to stakeholders?</t>
@@ -630,7 +630,7 @@
 • Reports comparing algorithm usage or key sizes across inventory snapshots
 • Metrics dashboards tracking adoption of PQC-ready algorithms or phase-out of deprecated ones
 • Trend analysis presentations linking system upgrades to reductions in quantum-exposed components
-• Forecast models projecting algorithm viability against quantum computing milestones ### Level 5 - Optimizing</t>
+• Forecast models projecting algorithm viability against quantum computing milestones</t>
   </si>
   <si>
     <t>How does your organization apply quantum vulnerability insights to improve cryptographic practices and standards?</t>
@@ -655,7 +655,7 @@
 • Post-assessment reviews resulting in updates to internal cryptographic configuration baselines
 • Documentation showing revisions to approved algorithm lists based on assessment trends
 • Change logs for secure coding guidelines reflecting common implementation issues
-• Automated rule updates in static analysis or CI/CD tools based on recurring crypto misuse patterns ## Practice 1.3: Cryptographic Dependency Mapping **Outcome**: A comprehensive understanding of how cryptographic components are interconnected throughout the organization, enabling coordinated migration planning that maintains system functionality while transitioning to quantum-resistant algorithms. ## Stream A: Foundation (60%)</t>
+• Automated rule updates in static analysis or CI/CD tools based on recurring crypto misuse patterns</t>
   </si>
   <si>
     <t>1.3: Cryptographic Dependency Mapping</t>
@@ -783,7 +783,7 @@
 • Scheduled reviews or audits that include validation and updates of cryptographic dependency documentation
 • Automated tools that detect new or modified cryptographic relationships and update dependency records in real time
 • Version-controlled repository or database showing historical changes to cryptographic dependencies
-• Dashboards or metrics tracking update frequency and data freshness of dependency records ## Stream B: Advanced (40%)</t>
+• Dashboards or metrics tracking update frequency and data freshness of dependency records</t>
   </si>
   <si>
     <t>How is cryptographic dependency information used to inform migration planning and operational risk management?</t>
@@ -808,7 +808,7 @@
 • Migration plans that include sequencing steps based on documented cryptographic dependencies
 • Risk assessments or threat models highlighting cascading failure potential from shared cryptographic components
 • Change approval workflows requiring dependency impact analysis for key rotations or algorithm upgrades
-• Dependency-aware fallback or rollback procedures defined in migration playbooks ### Level 2 - Developing</t>
+• Dependency-aware fallback or rollback procedures defined in migration playbooks</t>
   </si>
   <si>
     <t>How does your organization manage cryptographic dependencies in software build systems and code-signing infrastructure?</t>
@@ -883,7 +883,7 @@
 • Crypto dependency diagrams annotated with shared libraries, protocols, or trust anchors that highlight upgrade bottlenecks
 • Architecture review records identifying fragile crypto trust paths or legacy chokepoints
 • Complexity scores or dashboards tracking depth of cryptographic chains, shared asset reuse, and decoupling progress
-• Logs showing crypto-related changes that triggered cascading impacts across services ### Level 5 - Optimizing</t>
+• Logs showing crypto-related changes that triggered cascading impacts across services</t>
   </si>
   <si>
     <t>How are cryptographic dependencies tracked across CI/CD pipelines, shared libraries, and external APIs?</t>
@@ -908,8 +908,7 @@
 • Dependency files or manifests (e.g. SBOMs) listing cryptographic libraries and algorithms
 • Documentation of cryptographic interfaces to third-party APIs or managed services
 • Security controls in pipelines enforcing approved cryptographic algorithms for code signing and deployment
-• Automated tooling output showing real-time tracking or alerts on cryptographic changes in builds or dependencies
-• --- #  Dimension 2: Strategic Governance &amp; Risk Management (SGRM) *Understanding and cataloging organizational capabilities* ## Practice 2.1: Executive Leadership &amp; Policy Management **Outcome**: Clear leadership direction and robust policy framework for quantum risk management with appropriate governance structures. ## Stream A: Foundation (60%)</t>
+• Automated tooling output showing real-time tracking or alerts on cryptographic changes in builds or dependencies</t>
   </si>
   <si>
     <t>SGRM</t>
@@ -940,7 +939,7 @@
 • Executive charters or board minutes explicitly referencing quantum computing risks
 • Organizational charts or role definitions showing a named executive or officer responsible for quantum readiness
 • Governance frameworks or steering committee documents detailing mandates to oversee cryptographic transitions and quantum-safe planning
-• Strategic plans or roadmaps with timelines for achieving post-quantum cryptographic readiness approved by executive or board-level governance bodies ### Level 2 - Developing</t>
+• Strategic plans or roadmaps with timelines for achieving post-quantum cryptographic readiness approved by executive or board-level governance bodies</t>
   </si>
   <si>
     <t>How comprehensive is your quantum risk policy framework?</t>
@@ -1040,7 +1039,7 @@
 • Executive sponsorship of quantum research initiatives, pilots, or grants internally or through external partners (e.g., universities, consortia, or startups)
 • Innovation charters, working groups, or labs specifically focused on cryptographic modernization or quantum security experimentation
 • Budget allocations or strategic plans specifically earmarked for exploratory or pre-commercial quantum security technologies
-• Recognition or incentive programs that reward staff contributions to quantum-safe innovation (e.g., hackathons, patents, innovation KPIs) ## Stream B: Advanced (40%)</t>
+• Recognition or incentive programs that reward staff contributions to quantum-safe innovation (e.g., hackathons, patents, innovation KPIs)</t>
   </si>
   <si>
     <t>How is quantum risk integrated into organizational strategy and long-term planning?</t>
@@ -1087,7 +1086,7 @@
 • Documented policy review schedule specifying frequency and responsible roles for quantum-related updates
 • Change logs showing version history and rationale for updates to quantum risk policies
 • Integration with automated tooling or GRC platforms that track compliance or threat data and recommend or initiate policy updates
-• Training materials or rollout communications linked to recent policy revisions, showing that updates are operationalized across the organization ### Level 3 - Established</t>
+• Training materials or rollout communications linked to recent policy revisions, showing that updates are operationalized across the organization</t>
   </si>
   <si>
     <t>How is executive leadership kept informed and prepared to guide quantum security strategy?</t>
@@ -1162,7 +1161,7 @@
 • Membership in organizations like NIST, ETSI, ISO, IETF, or QSC and contributions to their standards
 • Participation in cross-sector exercises (e.g., financial or healthcare quantum risk pilots)
 • Published maturity models, playbooks, or cryptographic transition architectures
-• White papers, blogs, or public presentations on cryptographic transition strategies ## Practice 2.2: Risk Assessment &amp; Compliance Management **Outcome**: Systematic approach to identifying, assessing, and mitigating quantum risks with clear alignment to compliance requirements. ## Stream A: Foundation (60%)</t>
+• White papers, blogs, or public presentations on cryptographic transition strategies</t>
   </si>
   <si>
     <t>2.2: Risk Assessment &amp; Compliance Management</t>
@@ -1190,7 +1189,7 @@
 • Risk assessment documentation outlining methodology, data sources, and scoring models specific to quantum computing threats
 • Defined quantum-specific risk categories based on algorithm type, key size, asset exposure, data retention requirements, and business criticality
 • Application of Mosca’s Theorem or equivalent models to prioritize cryptographic migration timelines
-• Use of automated tools or platforms that continuously assess quantum vulnerability based on threat intelligence, algorithm deprecation updates, or system changes ### Level 2 - Developing</t>
+• Use of automated tools or platforms that continuously assess quantum vulnerability based on threat intelligence, algorithm deprecation updates, or system changes</t>
   </si>
   <si>
     <t>How automated is your quantum risk monitoring and integration into cryptographic transition planning?</t>
@@ -1240,7 +1239,7 @@
 • Documentation showing use of scoring models that combine algorithm type, key size, data sensitivity and exposure, and projected protection lifespan
 • Quantified assessments of critical systems that incorporate Mosca’s Theorem to evaluate urgency for quantum-safe migration
 • Business impact modeling reports linking cryptographic vulnerabilities to revenue streams, regulatory risk, or operational disruption
-• Integration of quantum risk exposure scores into cryptographic agility planning or executive decision-making frameworks ### Level 4 - Advanced</t>
+• Integration of quantum risk exposure scores into cryptographic agility planning or executive decision-making frameworks</t>
   </si>
   <si>
     <t>How do you validate the effectiveness of quantum risk controls?</t>
@@ -1290,7 +1289,7 @@
 • Documented process for integrating threat intelligence on PQC breakages, lattice attacks, or hybrid scheme vulnerabilities into risk models
 • Version-controlled risk framework with tracked revisions based on NIST PQC standardization or cryptanalysis developments
 • Use of quantum-aware scoring factors such as data lifespan, adversary capability growth, and cryptographic downgrade risks
-• Reports showing periodic reassessment of PQC migration priorities based on new quantum threat modeling scenarios ## Stream B: Advanced (40%)</t>
+• Reports showing periodic reassessment of PQC migration priorities based on new quantum threat modeling scenarios</t>
   </si>
   <si>
     <t>How mature is your quantum security compliance program?</t>
@@ -1315,7 +1314,7 @@
 • Audit reports verifying HSM compatibility with approved PQC algorithms and flagging unsupported devices
 • PKI policy documents covering hybrid certificates, short lifetimes, and post-quantum revocation practices
 • CI/CD pipeline scripts enforcing PQ-safe cryptographic configurations at build and test stages
-• Attestations confirming use of PQC algorithms in code signing and software release workflows ### Level 2 - Developing</t>
+• Attestations confirming use of PQC algorithms in code signing and software release workflows</t>
   </si>
   <si>
     <t>How does your organization adapt cryptographic practices in response to evolving quantum security standards and regulatory requirements?</t>
@@ -1415,7 +1414,7 @@
 • Control testing reports that document verification of quantum-safe cryptographic configurations (e.g., NIST-approved PQC algorithms, shortened key lifetimes)
 • CI/CD scripts or runtime scanners that flag cryptographic misconfigurations, including fallback usage or downgrade paths
 • Results from penetration tests or config audits showing quantum-relevant vulnerabilities and their remediation
-• Inclusion of PQC enforcement checks in third-party risk assessments or SOC audit mappings ## Practice 2.3: Third-Party &amp; Supply Chain Risk Management **Outcome**: Comprehensive approach to identifying and managing quantum-related risks in the supply chain and vendor ecosystem. ## Stream A: Foundation (60%)</t>
+• Inclusion of PQC enforcement checks in third-party risk assessments or SOC audit mappings</t>
   </si>
   <si>
     <t>2.3: Third-Party &amp; Supply Chain Risk Management</t>
@@ -1499,7 +1498,7 @@
     <t>How does your organization enforce and validate vendor cryptographic agility under real-world constraints?</t>
   </si>
   <si>
-    <t>**:** This examines your organization’s oversight of whether vendors can reliably perform cryptographic agility operations under realistic operational, hardware, and deployment constraints, including bandwidth limitations, embedded environments, or downtime-sensitive systems.</t>
+    <t>This examines your organization’s oversight of whether vendors can reliably perform cryptographic agility operations under realistic operational, hardware, and deployment constraints, including bandwidth limitations, embedded environments, or downtime-sensitive systems.</t>
   </si>
   <si>
     <t>No validation or enforcement of vendor cryptographic agility is performed</t>
@@ -1543,7 +1542,7 @@
 • Vendor questionnaires or technical due diligence checklists confirming HSM or TPM support for PQC-compatible key storage, signing, or key exchange functions
 • Documentation of hardware certification that includes post-quantum algorithm modules or firmware upgrade paths
 • Security architecture diagrams showing how the vendor’s systems manage key rotation, hybrid certs, or fallback enforcement using secure hardware
-• Audit reports or test results demonstrating the vendor’s ability to update cryptographic libraries and hardware integrations in response to PQC deprecation or algorithm updates ## Stream B: Advanced (40%)</t>
+• Audit reports or test results demonstrating the vendor’s ability to update cryptographic libraries and hardware integrations in response to PQC deprecation or algorithm updates</t>
   </si>
   <si>
     <t>How does your organization assess and manage quantum-related risks across its supply chain?</t>
@@ -1593,7 +1592,7 @@
 • Cryptographic risk assessment reports or scorecards for individual vendors, platforms, firmware, or services
 • Risk models incorporating technical details such as hardcoded algorithms, upgrade feasibility, or key handling limitations
 • Vendor-specific reports showing assessment of TLS endpoints, signing mechanisms, firmware cryptography, or dependency trees
-• Automated tools or dashboards that map technical quantum exposure across supply chain elements using configuration, telemetry, or SBOM data ### Level 3 - Established</t>
+• Automated tools or dashboards that map technical quantum exposure across supply chain elements using configuration, telemetry, or SBOM data</t>
   </si>
   <si>
     <t>How do you identify and prioritize supply chain systems that could delay or block enterprise cryptographic transitions?</t>
@@ -1668,8 +1667,7 @@
 • Published guidance, case studies, or tooling contributions related to quantum vendor risk management
 • Participation in industry forums or working groups focused on post-quantum supply chain security
 • Internal innovation programs or retrospectives aimed at improving vendor cryptographic assurance
-• Recognition, adoption, or citation of your vendor risk practices in external frameworks, toolkits, or standards
-• --- #  Dimension 3: Data Protection Engineering (DPE) *Understanding and cataloging organizational capabilities* #  Dimension 3: Data Protection Engineering (DPE) *Understanding and cataloging organizational capabilities* ## Purpose Design and implement quantum-resistant data protection controls throughout the data lifecycle. ## Strategic Value Ensures long-term protection of sensitive data against quantum threats Creates alignment between data sensitivity and appropriate quantum-resistant controls Establishes protection for data at rest, in transit, and in use Supports compliance with data protection regulations in a post-quantum environment Enables cryptographic agility across all data protection mechanisms Maintains data usability while transitioning to quantum-resistant algorithms ## Practice Areas ### Practice 3.1: Data Classification &amp; Protection Requirements **Outcome**: A comprehensive data protection framework that aligns protection measures with data sensitivity and quantum risk levels across the entire data lifecycle.</t>
+• Recognition, adoption, or citation of your vendor risk practices in external frameworks, toolkits, or standards</t>
   </si>
   <si>
     <t>DPE</t>
@@ -1919,7 +1917,7 @@
 • Performance test reports comparing encryption or key management overhead to system benchmarks or baseline configurations
 • Defined thresholds or performance budgets for latency, memory usage, or throughput related to data protection mechanisms
 • Simulation or testbed results showing how protection control choices impact performance in representative workloads
-• Analysis reports that identify performance bottlenecks tied to specific protection implementations or configuration states ### Practice 3.2: Storage Security &amp; Encryption Management **Outcome**: Robust storage security measures that ensure data confidentiality and integrity remains protected against quantum attacks throughout the data's storage lifetime.</t>
+• Analysis reports that identify performance bottlenecks tied to specific protection implementations or configuration states</t>
   </si>
   <si>
     <t>How does your organization ensure that symmetric encryption for sensitive stored data is secure against quantum algorithms?</t>
@@ -2169,7 +2167,7 @@
 • Strategy documents outlining long-term goals for improving storage encryption, key management, and lifecycle enforcement
 • Records of research, pilot projects, or POCs evaluating new cryptographic techniques or storage security technologies
 • Internal reviews identifying capability gaps and corresponding remediation or enhancement roadmaps
-• Adoption of advanced features (e.g., algorithm agility, dynamic rekeying, self-validating storage) in enterprise storage platforms ### Practice 3.3: Transit Security &amp; Protocol Management **Outcome**: Secure communications infrastructure that protects data in motion using quantum-resistant protocols and controls that maintain confidentiality and integrity.</t>
+• Adoption of advanced features (e.g., algorithm agility, dynamic rekeying, self-validating storage) in enterprise storage platforms</t>
   </si>
   <si>
     <t>How does your organization implement cryptographic protections within data-in-transit protocols?</t>
@@ -2419,8 +2417,7 @@
 • Documentation of upgrade plans that assess impact on legacy or third-party systems during cryptographic changes
 • Architecture diagrams or configuration files supporting dual-stack (e.g., hybrid) implementations in TLS or VPNs
 • Records of internal or vendor-supported interoperability testing for cryptographic transitions (e.g., new TLS libraries, PQ-ready clients)
-• Mitigation strategies to handle failures or incompatibility with older clients (e.g., logging, alerts, fallback policies) ## CMMC Alignment CMMC SC.1.175: Monitor, control, and protect organizational communications CMMC SC.2.179: Use encrypted sessions for the management of network devices CMMC MP.3.123: Mark media with necessary security markings and distribution limitations CMMC RM.2.143: Remediate vulnerabilities in accordance with risk assessments ## Integration with Other Dimensions **Inputs from CVI**: Cryptographic asset inventory informs protection needs **Inputs from SGRM**: Risk assessment results guide protection priorities **Outputs to ITR**: Protection requirements drive implementation planning **Outputs to ORC**: Protected services inform continuity planning **Outputs to WOE**: Protection technologies define skills requirements **Inputs from quantum computing monitoring**: Timeline updates for algorithm transitions **Outputs to vendor management**: Quantum-resistant requirements for data protection solutions ## Industry-Specific Considerations **Financial Services**: Payment card data, financial transactions, customer records, long-term financial agreements **Healthcare**: Protected health information, medical imaging, patient records, lifetime health data repositories **Government**: Classified information, citizen data, critical communications, national security information **Manufacturing**: Intellectual property, industrial designs, supply chain data, long-lifecycle product specifications ## Cryptographic Agility Framework Key management systems designed for algorithm transition Protocol selection and implementation supporting multiple algorithms Data format standards facilitating encryption algorithm changes Performance monitoring during cryptographic transitions Testing framework for validating cryptographic agility ## Quantum-Resistant Key Management Extended key lifecycle management for quantum era Strategies for secure key distribution in post-quantum environment Hybrid key approaches during transition periods Key rotation strategies aligned with quantum computing timeline Secure key storage resistant to retroactive decryption
-• -- #  Dimension 4: Implementation &amp; Technical Readiness (ITR) *Understanding and cataloging organizational capabilities* #  Dimension 4: Implementation &amp; Technical Readiness (ITR) *Understanding and cataloging organizational capabilities* ## Purpose Ensure technical capabilities and infrastructure are in place to implement and maintain quantum-resistant solutions. ## Strategic Value Provides a clear understanding of technical readiness for quantum-safe transition Establishes frameworks for planning and implementing quantum-resistant solutions Ensures quality and compliance of quantum-safe implementations Creates capability for ongoing testing and validation of quantum-resistant solutions Enables effective cryptographic agility through technical architecture Addresses performance considerations of post-quantum implementations ## Practice Areas ### Practice 4.1: Infrastructure Assessment &amp; Planning **Outcome**: A comprehensive understanding of infrastructure readiness and a clear roadmap for implementing quantum-resistant solutions across the technical environment.</t>
+• Mitigation strategies to handle failures or incompatibility with older clients (e.g., logging, alerts, fallback policies)</t>
   </si>
   <si>
     <t>ITR</t>
@@ -2673,7 +2670,7 @@
 • Participation in standards bodies (e.g., NIST, IETF, ETSI, ISO) specifically focused on algorithm agility, hybrid certificates, or PQC transition protocols
 • Involvement in pilot projects, testbeds, or proofs of concept that validate agile cryptographic standards (e.g., dual-algorithm TLS or certificate chains)
 • Open-source code, reference implementations, or deployment feedback influencing agility-related cryptographic standards
-• Active participation in interoperability workshops or benchmarking events for post-quantum or agile cryptographic protocols ### Practice 4.2: Implementation Capability Development **Outcome**: Well-defined technical capabilities and delivery processes to effectively implement quantum-resistant solutions across the organization.</t>
+• Active participation in interoperability workshops or benchmarking events for post-quantum or agile cryptographic protocols</t>
   </si>
   <si>
     <t>How does your organization define the technical capabilities required to support quantum-resistant implementation?</t>
@@ -2923,7 +2920,7 @@
 • CI/CD pipeline rules that enforce allowed algorithms, key lengths, or crypto library versions
 • Build scripts that reject deprecated cryptographic configurations or non-hybrid certificate chains
 • Rollback simulation that account for cryptographic failure or downgrade scenarios
-• Integration of SBOMs or dependency scanners flagging insecure or legacy crypto libraries before deployment ### Practice 4.3: Testing &amp; Validation Capabilities **Outcome**: Robust testing and validation frameworks that ensure quantum-resistant implementations meet security, performance, and compliance requirements.</t>
+• Integration of SBOMs or dependency scanners flagging insecure or legacy crypto libraries before deployment</t>
   </si>
   <si>
     <t>How comprehensive is your testing strategy for cryptographic transitions and quantum-resistant implementations?</t>
@@ -3173,13 +3170,7 @@
 • Participation in industry groups or standards bodies focused on cryptographic validation (e.g., NIST, ETSI, ISO, IETF)
 • Open-source contributions to cryptographic testing tools, validators, or benchmark suites
 • Publication of validation methodologies, test artifacts, or case studies used by peer organizations
-• Collaboration with vendors, researchers, or consortia to define shared validation practices or interoperability goals ## CMMC Alignment CMMC CA.2.159: Develop and implement plans of action designed to correct deficiencies CMMC CA.3.162: Employ a security assessment of enterprise software that has been developed internally CMMC CM.2.061: Establish and maintain baseline configurations of organizational systems CMMC RA.2.142: Scan for vulnerabilities in organizational systems and applications ## Integration with Other Dimensions **Inputs from CVI**: Cryptographic asset inventory informs implementation scope **Inputs from SGRM**: Governance requirements guide implementation approach **Inputs from DPE**: Protection requirements drive implementation specifications **Outputs to ORC**: Implementation details inform continuity planning **Outputs to WOE**: Implementation approaches define skills requirements **Outputs to vendor management**: Technical requirements for quantum-resistant solutions **Inputs from research**: Performance benchmarks for post-quantum algorithms ## Industry-Specific Considerations **Financial Services**: Payment systems, transaction processing, financial applications, high-performance trading systems **Healthcare**: Medical devices, health information systems, clinical applications, resource-constrained medical devices **Government**: Classified systems, agency applications, public services, cross-agency interoperability **Manufacturing**: Operational technology, industrial systems, supply chain applications, legacy industrial control systems ## Cryptographic Algorithm Performance Analysis Performance benchmarking for quantum-resistant algorithms Resource utilization analysis for different implementation approaches Impact assessment of larger key sizes and signature lengths Optimization techniques for constrained environments Network bandwidth impact analysis for larger cryptographic material ## Implementation Transition Strategies Phased implementation approaches for mission-critical systems Hybrid implementation patterns supporting cryptographic agility Fallback mechanisms for ensuring operational continuity Algorithm selection frameworks based on system requirements Testing methodologies for cryptographic transitions
-• -- ## Scoring Methodology The QRAMM assessment uses a 5-point scale where:
-• Each question is scored from 1-5 based on the selected maturity level
-• Practice scores are calculated as the average of all questions within that practice
-• Dimension scores are calculated as the average of all practices within that dimension
-• Overall QRAMM score is calculated as the average of all four dimension scores ## Assessment Completion This complete 120-question assessment provides comprehensive evaluation across all quantum readiness dimensions. For additional implementation guidance, please visit [https://qramm.org](https://qramm.org) or contact [qramm@csnp.org](mailto:qramm@csnp.org).
-• -- *This assessment is part of the QRAMM (Quantum Readiness Assurance Maturity Model) framework. For more information, visit https://qramm.org*</t>
+• Collaboration with vendors, researchers, or consortia to define shared validation practices or interoperability goals</t>
   </si>
   <si>
     <t>Full Name</t>
@@ -8636,12 +8627,12 @@
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10" t="str">
-        <f>IF(D2&gt;=3.5,"Advanced",IF(D2&gt;=2.5,"Established",IF(D2&gt;=1.5,"Developing","Basic")))</f>
-        <v>Basic</v>
+        <f>IF(D2="","-",IF(D2&gt;=3.5,"Advanced",IF(D2&gt;=2.5,"Established",IF(D2&gt;=1.5,"Developing","Basic"))))</f>
+        <v>-</v>
       </c>
       <c r="F2" s="11" t="str">
-        <f>ROUND((D2/4)*100,1)&amp;"%"</f>
-        <v>0%</v>
+        <f>IF(D2="","-",ROUND((D2/4)*100,1)&amp;"%")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -8656,12 +8647,12 @@
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12" t="str">
-        <f>IF(D3&gt;=3.5,"Advanced",IF(D3&gt;=2.5,"Established",IF(D3&gt;=1.5,"Developing","Basic")))</f>
-        <v>Basic</v>
+        <f>IF(D3="","-",IF(D3&gt;=3.5,"Advanced",IF(D3&gt;=2.5,"Established",IF(D3&gt;=1.5,"Developing","Basic"))))</f>
+        <v>-</v>
       </c>
       <c r="F3" s="13" t="str">
-        <f>ROUND((D3/4)*100,1)&amp;"%"</f>
-        <v>0%</v>
+        <f>IF(D3="","-",ROUND((D3/4)*100,1)&amp;"%")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -8676,12 +8667,12 @@
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14" t="str">
-        <f>IF(D4&gt;=3.5,"Advanced",IF(D4&gt;=2.5,"Established",IF(D4&gt;=1.5,"Developing","Basic")))</f>
-        <v>Basic</v>
+        <f>IF(D4="","-",IF(D4&gt;=3.5,"Advanced",IF(D4&gt;=2.5,"Established",IF(D4&gt;=1.5,"Developing","Basic"))))</f>
+        <v>-</v>
       </c>
       <c r="F4" s="15" t="str">
-        <f>ROUND((D4/4)*100,1)&amp;"%"</f>
-        <v>0%</v>
+        <f>IF(D4="","-",ROUND((D4/4)*100,1)&amp;"%")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -8696,12 +8687,12 @@
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16" t="str">
-        <f>IF(D5&gt;=3.5,"Advanced",IF(D5&gt;=2.5,"Established",IF(D5&gt;=1.5,"Developing","Basic")))</f>
-        <v>Basic</v>
+        <f>IF(D5="","-",IF(D5&gt;=3.5,"Advanced",IF(D5&gt;=2.5,"Established",IF(D5&gt;=1.5,"Developing","Basic"))))</f>
+        <v>-</v>
       </c>
       <c r="F5" s="17" t="str">
-        <f>ROUND((D5/4)*100,1)&amp;"%"</f>
-        <v>0%</v>
+        <f>IF(D5="","-",ROUND((D5/4)*100,1)&amp;"%")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -8714,17 +8705,17 @@
       <c r="C7" s="18" t="s">
         <v>899</v>
       </c>
-      <c r="D7" s="18" t="e">
-        <f>ROUND(AVERAGE(D2:D5),2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E7" s="18" t="e">
-        <f>IF(D7&gt;=3.5,"Advanced",IF(D7&gt;=2.5,"Established",IF(D7&gt;=1.5,"Developing","Basic")))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F7" s="18" t="e">
-        <f>ROUND((D7/4)*100,1)&amp;"%"</f>
-        <v>#DIV/0!</v>
+      <c r="D7" s="18" t="str">
+        <f>IF(COUNT(D2:D5)=0,"-",ROUND(AVERAGE(D2:D5),2))</f>
+        <v>-</v>
+      </c>
+      <c r="E7" s="18" t="str">
+        <f>IF(D7="-","-",IF(D7&gt;=3.5,"Advanced",IF(D7&gt;=2.5,"Established",IF(D7&gt;=1.5,"Developing","Basic"))))</f>
+        <v>-</v>
+      </c>
+      <c r="F7" s="18" t="str">
+        <f>IF(D7="-","-",ROUND((D7/4)*100,1)&amp;"%")</f>
+        <v>-</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
